--- a/data/trans_camb/P19C06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,06</t>
+          <t>-2,17; 0,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,82</t>
+          <t>-1,79; 0,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 3,74</t>
+          <t>-1,19; 3,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,28</t>
+          <t>-0,57; 1,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,03</t>
+          <t>-0,37; 2,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,71</t>
+          <t>-0,2; 1,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,52</t>
+          <t>-0,87; 0,53</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,15</t>
+          <t>-0,64; 1,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,82</t>
+          <t>-0,33; 1,95</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-87,73; 32,88</t>
+          <t>-88,99; 30,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 99,9</t>
+          <t>-84,14; 133,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-71,05; 460,12</t>
+          <t>-67,53; 445,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,05; 260,23</t>
+          <t>-45,26; 253,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-31,2; 385,7</t>
+          <t>-36,07; 419,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,26; 374,7</t>
+          <t>-22,93; 377,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-53,47; 69,09</t>
+          <t>-54,94; 70,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-41,62; 136,1</t>
+          <t>-44,52; 148,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 240,69</t>
+          <t>-26,51; 213,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,93</t>
+          <t>-0,53; 1,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 1,29</t>
+          <t>-0,34; 1,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,4</t>
+          <t>-0,89; 0,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,27</t>
+          <t>-0,41; 1,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,74</t>
+          <t>-0,83; 0,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 0,24</t>
+          <t>-1,07; 0,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,81</t>
+          <t>-0,3; 0,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,8</t>
+          <t>-0,3; 0,79</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,12</t>
+          <t>-0,78; 0,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-48,68; 170,49</t>
+          <t>-46,33; 190,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 244,78</t>
+          <t>-32,6; 232,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-67,25; 80,65</t>
+          <t>-65,98; 97,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,27; 168,12</t>
+          <t>-30,96; 176,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,33; 99,36</t>
+          <t>-50,95; 111,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 35,49</t>
+          <t>-65,35; 39,23</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 110,81</t>
+          <t>-24,7; 106,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 101,54</t>
+          <t>-25,09; 113,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 18,49</t>
+          <t>-58,77; 22,22</t>
         </is>
       </c>
     </row>
@@ -1114,42 +1114,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 0,97</t>
+          <t>-1,53; 0,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,64</t>
+          <t>-1,7; 0,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,61</t>
+          <t>-1,93; 1,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 1,62</t>
+          <t>-1,74; 1,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,96</t>
+          <t>-2,22; 1,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,17</t>
+          <t>-1,09; 1,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,93</t>
+          <t>-1,32; 0,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,56</t>
+          <t>-1,35; 0,56</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,05; 543,47</t>
+          <t>-100,0; 381,32</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-89,85; 395,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,85; 235,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-74,64; 217,76</t>
+          <t>-76,43; 234,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,74; 220,3</t>
+          <t>-70,11; 277,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,0; 132,12</t>
+          <t>-73,48; 129,21</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,48; 159,41</t>
+          <t>-58,09; 143,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-62,73; 123,03</t>
+          <t>-64,6; 130,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,47; 69,07</t>
+          <t>-63,56; 75,39</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 0,43</t>
+          <t>-0,65; 0,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 0,72</t>
+          <t>-0,45; 0,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,95</t>
+          <t>-0,21; 1,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 0,8</t>
+          <t>-0,33; 0,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,38</t>
+          <t>-0,6; 0,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,47</t>
+          <t>-0,29; 0,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 0,58</t>
+          <t>-0,27; 0,59</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,29</t>
+          <t>-0,57; 0,2</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,1; 57,78</t>
+          <t>-50,26; 52,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,17; 90,6</t>
+          <t>-34,7; 95,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,22; 44,51</t>
+          <t>-59,3; 44,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,2; 109,5</t>
+          <t>-14,7; 123,43</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 92,89</t>
+          <t>-25,1; 97,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,14; 47,79</t>
+          <t>-41,08; 53,01</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 53,05</t>
+          <t>-22,47; 56,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 61,99</t>
+          <t>-20,38; 62,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-38,55; 31,46</t>
+          <t>-43,31; 22,63</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C06-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P19C06-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,25</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,5</t>
+          <t>0,22</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,11</t>
+          <t>-2,08; 0,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,93</t>
+          <t>-1,82; 0,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 3,57</t>
+          <t>-1,44; 1,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,29</t>
+          <t>-0,46; 1,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,18</t>
+          <t>-0,23; 2,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,79</t>
+          <t>-0,3; 1,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,53</t>
+          <t>-0,87; 0,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 1,16</t>
+          <t>-0,56; 1,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,95</t>
+          <t>-0,55; 1,15</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>-16,19%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-88,99; 30,75</t>
+          <t>-91,36; 26,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-84,14; 133,71</t>
+          <t>-85,27; 118,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 445,5</t>
+          <t>-76,06; 191,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,26; 253,2</t>
+          <t>-38,84; 268,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,07; 419,52</t>
+          <t>-30,81; 503,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-22,93; 377,06</t>
+          <t>-28,8; 281,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-54,94; 70,97</t>
+          <t>-53,8; 70,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,52; 148,84</t>
+          <t>-40,93; 152,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,51; 213,36</t>
+          <t>-39,44; 138,13</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,35</t>
+          <t>-0,27</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,24</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,0</t>
+          <t>-0,58; 0,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,22</t>
+          <t>-0,32; 1,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,46</t>
+          <t>-0,84; 0,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 1,29</t>
+          <t>-0,45; 1,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,82</t>
+          <t>-0,84; 0,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 0,25</t>
+          <t>-1,05; 0,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,87</t>
+          <t>-0,29; 0,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,79</t>
+          <t>-0,27; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 0,15</t>
+          <t>-0,76; 0,2</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-25,45%</t>
+          <t>-23,41%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-30,84%</t>
+          <t>-23,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-28,69%</t>
+          <t>-23,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-46,33; 190,21</t>
+          <t>-49,87; 164,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,6; 232,83</t>
+          <t>-29,25; 240,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 97,59</t>
+          <t>-66,3; 85,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,96; 176,69</t>
+          <t>-32,43; 183,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,95; 111,55</t>
+          <t>-52,37; 111,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,35; 39,23</t>
+          <t>-63,39; 52,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 106,03</t>
+          <t>-23,5; 113,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 113,77</t>
+          <t>-23,19; 110,03</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,77; 22,22</t>
+          <t>-53,53; 30,89</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-0,31</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,68</t>
+          <t>-1,16; 1,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,98</t>
+          <t>-1,58; 0,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 0,66</t>
+          <t>-1,74; 0,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 1,66</t>
+          <t>-2,04; 1,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 1,82</t>
+          <t>-1,75; 1,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,0</t>
+          <t>-2,0; 0,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,12</t>
+          <t>-1,19; 1,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,91</t>
+          <t>-1,26; 0,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,56</t>
+          <t>-1,31; 0,52</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-31,89%</t>
+          <t>-36,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-17,64%</t>
+          <t>-17,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-21,34%</t>
+          <t>-22,99%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 381,32</t>
+          <t>-81,13; 426,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,49; 269,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-76,43; 234,97</t>
+          <t>-76,59; 220,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 277,59</t>
+          <t>-68,85; 239,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,48; 129,21</t>
+          <t>-66,81; 141,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 143,37</t>
+          <t>-59,04; 154,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,6; 130,02</t>
+          <t>-63,25; 131,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 75,39</t>
+          <t>-65,48; 73,29</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>-0,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 0,43</t>
+          <t>-0,73; 0,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,74</t>
+          <t>-0,52; 0,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 0,33</t>
+          <t>-0,87; 0,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,0</t>
+          <t>-0,27; 0,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,83</t>
+          <t>-0,37; 0,82</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 0,45</t>
+          <t>-0,57; 0,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,53</t>
+          <t>-0,32; 0,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,59</t>
+          <t>-0,29; 0,56</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,2</t>
+          <t>-0,53; 0,19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-24,22%</t>
+          <t>-29,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-6,44%</t>
+          <t>-2,96%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-14,94%</t>
+          <t>-15,72%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,26; 52,5</t>
+          <t>-53,46; 56,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,7; 95,31</t>
+          <t>-38,3; 85,81</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 44,89</t>
+          <t>-59,63; 31,3</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,7; 123,43</t>
+          <t>-20,48; 116,48</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 97,9</t>
+          <t>-26,05; 95,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 53,01</t>
+          <t>-38,82; 51,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,47; 56,26</t>
+          <t>-25,56; 53,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 62,65</t>
+          <t>-21,97; 62,0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,31; 22,63</t>
+          <t>-39,44; 21,19</t>
         </is>
       </c>
     </row>
